--- a/doc/help_dialogs/Input_files/s7.xlsx
+++ b/doc/help_dialogs/Input_files/s7.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Modbus" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="S7" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">The PID Control dialog can operate a connected PID using the given PID registers to set the p-i-d parameters and the set value (SV). S7 commands can be specified to turn the PID on and off from that PID Control dialog. See the help page in the Events Dialog for documentation of available S7 write commands.</t>
   </si>
   <si>
-    <t xml:space="preserve">The Scan button opens a simple MODBUS scanner to search for data holding registers in the connected device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refer to the User Manual of your MODBUS device for information specific to the setup required for your device.</t>
+    <t xml:space="preserve">The Scan button opens a simple S7 scanner to search for data holding registers in the connected device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refer to the User Manual of your S7 device for information specific to the setup required for your device.</t>
   </si>
 </sst>
 </file>
